--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSecuritiesAccount001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSecuritiesAccount001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14550" windowHeight="4005"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>证券账户账号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,6 +42,10 @@
   </si>
   <si>
     <t>账户来源</t>
+  </si>
+  <si>
+    <t>交易编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -104,7 +108,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -146,7 +150,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -181,7 +185,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -390,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="29.25" customWidth="1"/>
@@ -400,7 +404,7 @@
     <col min="5" max="5" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,6 +425,9 @@
       </c>
       <c r="G1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSecuritiesAccount001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSecuritiesAccount001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14550" windowHeight="4005"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14550" windowHeight="4010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,17 +42,18 @@
   </si>
   <si>
     <t>账户来源</t>
-  </si>
-  <si>
-    <t>交易编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易编码</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,6 +67,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -395,16 +402,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.25" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="3" width="29.875" customWidth="1"/>
-    <col min="4" max="4" width="28.25" customWidth="1"/>
-    <col min="5" max="5" width="26.875" customWidth="1"/>
+    <col min="1" max="1" width="29.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.90625" customWidth="1"/>
+    <col min="4" max="4" width="28.26953125" customWidth="1"/>
+    <col min="5" max="5" width="26.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +447,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -450,7 +457,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
